--- a/03_Prototyping/Potential_User_Evaluation_Team-Travi.xlsx
+++ b/03_Prototyping/Potential_User_Evaluation_Team-Travi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lh/Documents/University/University OAS Munich Business/7. Semester/7.1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63D1134C-58C3-294D-8CD3-DD096598B90D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA8E9627-F61D-48C3-9CAC-C6238B19C1DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{E40F4BC5-921B-0440-B11F-BCB11A63A909}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E40F4BC5-921B-0440-B11F-BCB11A63A909}"/>
   </bookViews>
   <sheets>
     <sheet name="Feedback" sheetId="1" r:id="rId1"/>
@@ -92,9 +92,6 @@
     <t>Could add an explore tab with trending or seasonal spots.</t>
   </si>
   <si>
-    <t>The UI was very clean. Felt like something I’d use while commuting.</t>
-  </si>
-  <si>
     <t>Yes, it clearly helps me plan trips and bookmark ideas effortlessly.</t>
   </si>
   <si>
@@ -122,9 +119,6 @@
     <t>Maybe add a comment section for each destination to get peer reviews.</t>
   </si>
   <si>
-    <t>Navigation was simple, and I liked how fast it loaded.</t>
-  </si>
-  <si>
     <t>Yes, it’s made for people like me who travel often and plan quickly.</t>
   </si>
   <si>
@@ -137,9 +131,6 @@
     <t>Calendar sync or export to PDF would be useful.</t>
   </si>
   <si>
-    <t>Nice layout, and it felt very welcoming with the ‘Hey’ message.</t>
-  </si>
-  <si>
     <t>Yes, especially the way it saves places and accommodations I like.</t>
   </si>
   <si>
@@ -183,6 +174,15 @@
   </si>
   <si>
     <t>Interviewee 4: Male, 41, finance consultant</t>
+  </si>
+  <si>
+    <t>The UI was clean.</t>
+  </si>
+  <si>
+    <t>Nice layout</t>
+  </si>
+  <si>
+    <t>Navigation was simple.</t>
   </si>
 </sst>
 </file>
@@ -265,7 +265,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -336,12 +336,8 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -661,17 +657,17 @@
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="C1:AM10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="41.5" customWidth="1"/>
-    <col min="4" max="4" width="66.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="66.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="72" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="77.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="79" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="60" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:39" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:39" ht="24" x14ac:dyDescent="0.4">
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
@@ -712,7 +708,7 @@
       <c r="AL1" s="2"/>
       <c r="AM1" s="2"/>
     </row>
-    <row r="3" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="3" spans="3:39" x14ac:dyDescent="0.25">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -732,7 +728,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="4" spans="3:39" x14ac:dyDescent="0.25">
       <c r="C4" s="4" t="s">
         <v>7</v>
       </c>
@@ -752,124 +748,124 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="3:39" x14ac:dyDescent="0.25">
       <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>22</v>
-      </c>
     </row>
-    <row r="6" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="3:39" x14ac:dyDescent="0.25">
       <c r="C6" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="4" t="s">
+    </row>
+    <row r="7" spans="3:39" x14ac:dyDescent="0.25">
+      <c r="C7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="F7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="7" spans="3:39" x14ac:dyDescent="0.2">
-      <c r="C7" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="3:39" x14ac:dyDescent="0.25">
       <c r="C8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="9" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="3:39" x14ac:dyDescent="0.25">
       <c r="C9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>42</v>
-      </c>
     </row>
-    <row r="10" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="3:39" x14ac:dyDescent="0.25">
       <c r="C10" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/03_Prototyping/Potential_User_Evaluation_Team-Travi.xlsx
+++ b/03_Prototyping/Potential_User_Evaluation_Team-Travi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lh/Library/Mobile Documents/com~apple~CloudDocs/Documents/University/University OAS Munich Business/7. Semester/7.1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA8E9627-F61D-48C3-9CAC-C6238B19C1DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5E655F-28F3-1747-9E88-ABA6B54B3CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E40F4BC5-921B-0440-B11F-BCB11A63A909}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{E40F4BC5-921B-0440-B11F-BCB11A63A909}"/>
   </bookViews>
   <sheets>
     <sheet name="Feedback" sheetId="1" r:id="rId1"/>
@@ -77,112 +77,112 @@
     <t>Interviewee 7: Female, 31, marketing lead</t>
   </si>
   <si>
-    <t>Looks sleek and modern. It felt like a finished app.</t>
-  </si>
-  <si>
-    <t>Yes, it’s obvious this is for travelers looking to plan or discover trips quickly.</t>
-  </si>
-  <si>
-    <t>I liked the swipeable destination cards. Super engaging. Everything made sense.</t>
-  </si>
-  <si>
-    <t>I usually scroll Instagram and Google random blogs. This is way more focused.</t>
-  </si>
-  <si>
-    <t>Could add an explore tab with trending or seasonal spots.</t>
-  </si>
-  <si>
-    <t>Yes, it clearly helps me plan trips and bookmark ideas effortlessly.</t>
-  </si>
-  <si>
-    <t>The liked destinations and accommodations feature was very helpful.</t>
-  </si>
-  <si>
-    <t>Normally I just use booking.com and screenshots. This brings it all together.</t>
-  </si>
-  <si>
-    <t>Could integrate flight deals or a link to compare prices.</t>
-  </si>
-  <si>
-    <t>It was fun! I liked swiping through cities and hotels.</t>
-  </si>
-  <si>
-    <t>Yes, I understood I can build my travel wishlist easily.</t>
-  </si>
-  <si>
-    <t>The heart/favorite button was clear and satisfying to use.</t>
-  </si>
-  <si>
-    <t>Pinterest and TikTok are what I use now — this is more organized.</t>
-  </si>
-  <si>
-    <t>Maybe add a comment section for each destination to get peer reviews.</t>
-  </si>
-  <si>
-    <t>Yes, it’s made for people like me who travel often and plan quickly.</t>
-  </si>
-  <si>
-    <t>The group feature caught my eye — seems ideal for trip planning.</t>
-  </si>
-  <si>
-    <t>I use Google Docs to plan trips with friends — this is way easier.</t>
-  </si>
-  <si>
-    <t>Calendar sync or export to PDF would be useful.</t>
-  </si>
-  <si>
-    <t>Yes, especially the way it saves places and accommodations I like.</t>
-  </si>
-  <si>
-    <t>I liked how I could swipe through hotels and destinations in one place.</t>
-  </si>
-  <si>
-    <t>Normally I go back and forth between tabs — this centralizes everything.</t>
-  </si>
-  <si>
-    <t>Would love multi-language support for non-native speakers.</t>
-  </si>
-  <si>
-    <t>Minimalist design — big win. No clutter.</t>
-  </si>
-  <si>
-    <t>Yes, the whole concept of swiping and saving places is super intuitive.</t>
-  </si>
-  <si>
-    <t>The visual cards and categories were easy to scroll and understand.</t>
-  </si>
-  <si>
-    <t>I usually plan trips with Airbnb and Apple Notes. This was smoother.</t>
-  </si>
-  <si>
-    <t>A filter for budget or travel style (adventure, romantic, etc.) could help.</t>
-  </si>
-  <si>
-    <t>Design felt premium. I’d recommend it to my team for travel planning.</t>
-  </si>
-  <si>
-    <t>Yes, it’s obvious that it’s about personalizing your trips visually.</t>
-  </si>
-  <si>
-    <t>Liked accommodations and the like/dislike flow. It’s user-centric.</t>
-  </si>
-  <si>
-    <t>We usually email options back and forth — this cuts that out.</t>
-  </si>
-  <si>
-    <t>Add a comparison feature to choose between liked options.</t>
-  </si>
-  <si>
     <t>Interviewee 4: Male, 41, finance consultant</t>
   </si>
   <si>
-    <t>The UI was clean.</t>
-  </si>
-  <si>
-    <t>Nice layout</t>
-  </si>
-  <si>
-    <t>Navigation was simple.</t>
+    <t>Design is modern and easy on the eyes. Felt inviting.</t>
+  </si>
+  <si>
+    <t>Yes, I understood that it’s about collecting destinations I like.</t>
+  </si>
+  <si>
+    <t>The swipe cards were nice, but after a few swipes it started to feel repetitive.</t>
+  </si>
+  <si>
+    <t>I usually search on Instagram and save posts. This was simpler to use.</t>
+  </si>
+  <si>
+    <t>Maybe introduce categories or filters so it doesn’t feel too endless.</t>
+  </si>
+  <si>
+    <t>The layout was clear, and the dark mode is a good touch.</t>
+  </si>
+  <si>
+    <t>Yes, the purpose is clear — it's a place to save and explore trip ideas.</t>
+  </si>
+  <si>
+    <t>Saving liked hotels and destinations is helpful, though some cards load slowly.</t>
+  </si>
+  <si>
+    <t>I use booking.com and note ideas in WhatsApp. This makes it more visual.</t>
+  </si>
+  <si>
+    <t>Add a way to track estimated costs or compare options side by side.</t>
+  </si>
+  <si>
+    <t>Fun and fresh interface. Felt social-media-like, which I liked.</t>
+  </si>
+  <si>
+    <t>Yes, it's like building a travel mood board.</t>
+  </si>
+  <si>
+    <t>The heart icon made it easy to remember my favorites. Some destinations had too little info though.</t>
+  </si>
+  <si>
+    <t>Pinterest and TikTok are more visual, but this felt more purposeful.</t>
+  </si>
+  <si>
+    <t>Consider adding videos or more user-generated photos for each place.</t>
+  </si>
+  <si>
+    <t>Interface is okay. Nothing confusing, but nothing super new either.</t>
+  </si>
+  <si>
+    <t>Mostly, yes — although I wasn’t sure what happens after liking a trip.</t>
+  </si>
+  <si>
+    <t>I liked the group section, but I didn't try it fully. The swipe flow got a bit tiring.</t>
+  </si>
+  <si>
+    <t>I use spreadsheets and Google Docs for trip planning — this is faster but less detailed.</t>
+  </si>
+  <si>
+    <t>It would help to let users plan a draft itinerary after saving a few places.</t>
+  </si>
+  <si>
+    <t>I liked the greeting message and layout. Felt friendly.</t>
+  </si>
+  <si>
+    <t>Yes, it’s clear you’re building your travel preferences visually.</t>
+  </si>
+  <si>
+    <t>Swiping through destinations and hotels was easy and intuitive.</t>
+  </si>
+  <si>
+    <t>Normally I switch between tabs and apps. This puts things in one place.</t>
+  </si>
+  <si>
+    <t>Multi-language content would really help — not everything felt localized.</t>
+  </si>
+  <si>
+    <t>Nice minimalist interface. Clean and not overloaded.</t>
+  </si>
+  <si>
+    <t>Yes, it’s all about quick discovery and shortlisting trips.</t>
+  </si>
+  <si>
+    <t>The visual design and swipe experience were fluid. A bit too image-heavy sometimes.</t>
+  </si>
+  <si>
+    <t>I usually use Notion for trip ideas. This feels lighter and quicker.</t>
+  </si>
+  <si>
+    <t>Let me set trip dates and maybe sync to calendar later.</t>
+  </si>
+  <si>
+    <t>Looks polished. Could be useful for team retreat planning.</t>
+  </si>
+  <si>
+    <t>Yes, it's clearly focused on individual preferences and shortlists.</t>
+  </si>
+  <si>
+    <t>Liked the like/dislike interaction. Some icons could be bigger on smaller screens.</t>
+  </si>
+  <si>
+    <t>Usually I collect links in a shared doc. This is more engaging.</t>
+  </si>
+  <si>
+    <t>Would be helpful to add short reviews or travel tips under each card.</t>
   </si>
 </sst>
 </file>
@@ -265,7 +265,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -337,7 +337,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -657,17 +657,17 @@
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="C1:AM10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="41.5" customWidth="1"/>
-    <col min="4" max="4" width="66.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="66.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="72" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="77.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="81.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="79" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="60" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:39" ht="24" x14ac:dyDescent="0.4">
+    <row r="1" spans="3:39" ht="24" x14ac:dyDescent="0.3">
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
@@ -708,7 +708,7 @@
       <c r="AL1" s="2"/>
       <c r="AM1" s="2"/>
     </row>
-    <row r="3" spans="3:39" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -728,144 +728,144 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="3:39" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C4" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="5" spans="3:39" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="6" spans="3:39" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C6" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
-    <row r="7" spans="3:39" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C7" s="4" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
-    <row r="8" spans="3:39" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="9" spans="3:39" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="10" spans="3:39" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C10" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
